--- a/01_data/02_output_data/02_unidirectional_results/01_paper_IAEE/02_prepared_results/output_2024_prepared.xlsx
+++ b/01_data/02_output_data/02_unidirectional_results/01_paper_IAEE/02_prepared_results/output_2024_prepared.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studentcbs-my.sharepoint.com/personal/mar_eco_cbs_dk/Documents/Desktop/hydrogen_grid/01_data/02_output_data/02_unidirectional_results/01_paper_IAEE/02_prepared_results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{582356F6-DDAC-4D56-BFEF-9D697B88CFEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{582356F6-DDAC-4D56-BFEF-9D697B88CFEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{921217C5-CC98-4C2C-8F55-4EC54A825F0A}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw" sheetId="1" r:id="rId1"/>
@@ -1478,15 +1478,6 @@
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-    </dxf>
-    <dxf>
       <border outline="0">
         <bottom style="thick">
           <color theme="0"/>
@@ -1526,6 +1517,15 @@
         <top/>
         <bottom/>
       </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
@@ -1873,10 +1873,10 @@
   <autoFilter ref="A1:C17" xr:uid="{3417075B-B51B-429B-8BA8-43E190BF8519}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{A239A1DC-0210-4956-ABE7-EF6CDA5A30E2}" name="Edge"/>
-    <tableColumn id="2" xr3:uid="{322E7DE0-B95E-46AC-9403-C71D0E63B73A}" name="Flow (GWh)" dataDxfId="2">
+    <tableColumn id="2" xr3:uid="{322E7DE0-B95E-46AC-9403-C71D0E63B73A}" name="Flow (GWh)" dataDxfId="6">
       <calculatedColumnFormula>VLOOKUP(LNG_Import_use!$A2,Raw!$C$3:$E$429,2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{E19B88D8-3893-4610-AB1D-CF00C32B1D5C}" name="Share" dataDxfId="1">
+    <tableColumn id="3" xr3:uid="{E19B88D8-3893-4610-AB1D-CF00C32B1D5C}" name="Share" dataDxfId="5">
       <calculatedColumnFormula>VLOOKUP(LNG_Import_use!$A2,Raw!$C$3:$E$429,3,FALSE)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1889,7 +1889,7 @@
   <autoFilter ref="A1:B19" xr:uid="{A8372A6F-EB83-42B1-A6B1-D9A865C31E2A}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{D3B0A0F4-AE4B-4C05-803A-8265FB2E0BEC}" name="Edge"/>
-    <tableColumn id="2" xr3:uid="{3D272239-DFA1-4C23-990B-17340DB0F202}" name="Flow (GWh)" dataDxfId="6">
+    <tableColumn id="2" xr3:uid="{3D272239-DFA1-4C23-990B-17340DB0F202}" name="Flow (GWh)" dataDxfId="4">
       <calculatedColumnFormula>SUMIFS(Raw!$D$2:$D$371,Raw!$C$2:$C$371,"*"&amp;LNG_Sources!$A2&amp;"*")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1898,11 +1898,11 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{1122FFF2-C470-41D5-B466-2B2A16A0702F}" name="Table7" displayName="Table7" ref="D1:E6" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{1122FFF2-C470-41D5-B466-2B2A16A0702F}" name="Table7" displayName="Table7" ref="D1:E6" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1">
   <autoFilter ref="D1:E6" xr:uid="{1122FFF2-C470-41D5-B466-2B2A16A0702F}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{4B792274-18C2-4C26-B54A-695915F3118E}" name="Region"/>
-    <tableColumn id="2" xr3:uid="{46C98E86-4B19-4A99-BF1A-17F24AC916F1}" name="Flow (GWh)" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{46C98E86-4B19-4A99-BF1A-17F24AC916F1}" name="Flow (GWh)" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1913,7 +1913,7 @@
   <autoFilter ref="A1:B37" xr:uid="{8121B5DA-0937-487A-A3DF-77ACBB8999F9}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{03B06CF4-5F36-4B7E-8CC9-8D06BB4532D5}" name="Edge"/>
-    <tableColumn id="2" xr3:uid="{1AD1E774-B856-4665-89D5-9C7DC08BC3A8}" name="Flow (GWh)" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{1AD1E774-B856-4665-89D5-9C7DC08BC3A8}" name="Flow (GWh)" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9991,7 +9991,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD2D411B-08D5-4798-8AA5-FBD73D4A6C09}">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24.90625" customWidth="1"/>
@@ -9999,7 +9999,7 @@
     <col min="5" max="5" width="12.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -10013,7 +10013,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>222</v>
       </c>
@@ -10027,8 +10027,9 @@
         <f>SUMIF(Table6[Edge],"*AF*",Table6[Flow (GWh)])</f>
         <v>292335.82209085295</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F2" s="5"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>395</v>
       </c>
@@ -10043,7 +10044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>337</v>
       </c>
@@ -10058,7 +10059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>353</v>
       </c>
@@ -10073,7 +10074,7 @@
         <v>3106.5989325080009</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>98</v>
       </c>
@@ -10088,7 +10089,7 @@
         <v>1338185.0543291932</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>88</v>
       </c>
@@ -10096,7 +10097,7 @@
         <v>81491.87295725508</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>93</v>
       </c>
@@ -10104,7 +10105,7 @@
         <v>60574</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>356</v>
       </c>
@@ -10112,7 +10113,7 @@
         <v>43774.399641264652</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>107</v>
       </c>
@@ -10120,7 +10121,7 @@
         <v>36490.417710000002</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>396</v>
       </c>
@@ -10128,7 +10129,7 @@
         <v>25402</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>397</v>
       </c>
@@ -10136,7 +10137,7 @@
         <v>11669.450833333331</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>398</v>
       </c>
@@ -10144,7 +10145,7 @@
         <v>7494.6891249999999</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>399</v>
       </c>
@@ -10152,7 +10153,7 @@
         <v>3613.770355847626</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>242</v>
       </c>
@@ -10160,7 +10161,7 @@
         <v>155831.5</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>301</v>
       </c>
